--- a/data/externalStats/File1/RPT_RPT5713512752455CZ_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT5713512752455CZ_externalStats.xlsx
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>5520.587381943595</v>
+        <v>5520.587381943594</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>9.113706901155732</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>5138.937154405056</v>
+        <v>5138.937154405055</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>732.6670235945372</v>
+        <v>732.667023594537</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1562.181632578948</v>
+        <v>1562.181632578949</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>7.487248693337843</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>774.5378194108405</v>
+        <v>774.5378194108404</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>4.506520365848544</v>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>42512.23371758816</v>
+        <v>42512.23371758815</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>41.3512867871618</v>
@@ -3714,7 +3714,7 @@
         <v>15991.84448858188</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>34.17181086340696</v>
+        <v>34.17181086340697</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>7439.915137529334</v>
+        <v>7439.915137529335</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>13.63594514274421</v>
@@ -4002,10 +4002,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R54" s="131" t="n">
         <v>15.54712347542384</v>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -4326,7 +4326,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>0</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>10.9692656257673</v>
@@ -4671,13 +4671,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -4716,49 +4716,49 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>39.09953185359954</v>
+        <v>39.09953185359959</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98857189711013</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.11273231079224</v>
+        <v>32.11273231079223</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20.51692362463237</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>26.7744912852941</v>
+        <v>26.77449128529413</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4806,10 +4806,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -4821,10 +4821,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -5127,19 +5127,19 @@
         <v>171</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>169.749838119715</v>
+        <v>169.7498381197151</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>17.77149025158941</v>
@@ -5157,7 +5157,7 @@
         <v>161.058135532108</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>12.81966845609603</v>
@@ -6616,10 +6616,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R90" s="131" t="n">
         <v>15.54712347542384</v>
@@ -6643,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
     </row>
     <row r="91">
@@ -6884,7 +6884,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>0</v>
@@ -6905,7 +6905,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -7152,7 +7152,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>10.9692656257673</v>
@@ -7173,13 +7173,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
     </row>
     <row r="99">
@@ -7204,49 +7204,49 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>44.49156992393183</v>
+        <v>44.49156992393188</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.91479957144558</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.0389599851277</v>
+        <v>39.03895998512768</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>33.98642467644335</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>40.24399233710508</v>
+        <v>40.24399233710511</v>
       </c>
     </row>
     <row r="100">
@@ -7280,10 +7280,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -7295,10 +7295,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7543,16 +7543,16 @@
         <v>171</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>178.7726587222605</v>
@@ -7573,7 +7573,7 @@
         <v>172.8909201642285</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>12.81966845609603</v>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>51479.2874751646</v>
+        <v>51479.28747516461</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>42.88056699746012</v>
@@ -10518,10 +10518,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R54" s="131" t="n">
         <v>15.54712347542384</v>
@@ -10545,7 +10545,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -10842,7 +10842,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>0</v>
@@ -10863,7 +10863,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>10.9692656257673</v>
@@ -11187,13 +11187,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -11232,49 +11232,49 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>39.09953185359954</v>
+        <v>39.09953185359959</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98857189711013</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.11273231079224</v>
+        <v>32.11273231079223</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20.51692362463237</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>26.7744912852941</v>
+        <v>26.77449128529413</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11322,10 +11322,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -11337,10 +11337,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11634,19 +11634,19 @@
         <v>171</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>169.749838119715</v>
+        <v>169.7498381197151</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>17.77149025158941</v>
@@ -11664,7 +11664,7 @@
         <v>161.058135532108</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>12.81966845609603</v>
@@ -11690,7 +11690,7 @@
         <v>0</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>65.65184583143797</v>
+        <v>65.65184583143798</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -13131,10 +13131,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R90" s="131" t="n">
         <v>15.54712347542384</v>
@@ -13158,7 +13158,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
     </row>
     <row r="91">
@@ -13399,7 +13399,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>0</v>
@@ -13420,7 +13420,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -13667,7 +13667,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>10.9692656257673</v>
@@ -13688,13 +13688,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
     </row>
     <row r="99">
@@ -13719,49 +13719,49 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>44.49156992393183</v>
+        <v>44.49156992393188</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.91479957144558</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.0389599851277</v>
+        <v>39.03895998512768</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>33.98642467644335</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>40.24399233710508</v>
+        <v>40.24399233710511</v>
       </c>
     </row>
     <row r="100">
@@ -13795,10 +13795,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -13810,10 +13810,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -14058,16 +14058,16 @@
         <v>171</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>178.7726587222605</v>
@@ -14088,7 +14088,7 @@
         <v>172.8909201642285</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>12.81966845609603</v>
@@ -15136,7 +15136,7 @@
         <v>64043.47173804005</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>51.41716743555845</v>
+        <v>51.41716743555844</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>624.3542920536846</v>
+        <v>624.3542920536847</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>1.947948910730224</v>
@@ -16745,7 +16745,7 @@
         <v>15342.71504250832</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>32.37441038664758</v>
+        <v>32.37441038664759</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -16791,7 +16791,7 @@
         <v>6048.064903563136</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>9.374396464881979</v>
+        <v>9.374396464881981</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -17033,10 +17033,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R54" s="131" t="n">
         <v>15.54712347542384</v>
@@ -17060,7 +17060,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -17357,7 +17357,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>0</v>
@@ -17378,7 +17378,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -17681,7 +17681,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>10.9692656257673</v>
@@ -17702,13 +17702,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -17747,49 +17747,49 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>39.09953185359954</v>
+        <v>39.09953185359959</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98857189711013</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.11273231079224</v>
+        <v>32.11273231079223</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20.51692362463237</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>26.7744912852941</v>
+        <v>26.77449128529413</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17837,10 +17837,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -17852,10 +17852,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -18149,19 +18149,19 @@
         <v>171</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>169.749838119715</v>
+        <v>169.7498381197151</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>17.77149025158941</v>
@@ -18179,7 +18179,7 @@
         <v>161.058135532108</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>12.81966845609603</v>
@@ -19638,10 +19638,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R90" s="131" t="n">
         <v>15.54712347542384</v>
@@ -19665,7 +19665,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
     </row>
     <row r="91">
@@ -19906,7 +19906,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>0</v>
@@ -19927,7 +19927,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -20174,7 +20174,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>10.9692656257673</v>
@@ -20195,13 +20195,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
     </row>
     <row r="99">
@@ -20226,49 +20226,49 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>44.49156992393183</v>
+        <v>44.49156992393188</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.91479957144558</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.0389599851277</v>
+        <v>39.03895998512768</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>33.98642467644335</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>40.24399233710508</v>
+        <v>40.24399233710511</v>
       </c>
     </row>
     <row r="100">
@@ -20302,10 +20302,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -20317,10 +20317,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20565,16 +20565,16 @@
         <v>171</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>178.7726587222605</v>
@@ -20595,7 +20595,7 @@
         <v>172.8909201642285</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>12.81966845609603</v>
@@ -21794,7 +21794,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>9.116896294001295</v>
@@ -22025,7 +22025,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>3023.486740610278</v>
+        <v>3023.486740610279</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>6.654422619106247</v>
@@ -23206,7 +23206,7 @@
         <v>78879.6483755581</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>68.10200542396778</v>
+        <v>68.10200542396777</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -23265,10 +23265,10 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>9.284039392724651</v>
+        <v>9.284039392724653</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -23467,7 +23467,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>3023.486740610278</v>
+        <v>3023.486740610279</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>6.654422619106247</v>
@@ -23510,10 +23510,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R54" s="131" t="n">
         <v>15.54712347542384</v>
@@ -23537,7 +23537,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -23834,7 +23834,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>0</v>
@@ -23855,7 +23855,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -24158,7 +24158,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>10.9692656257673</v>
@@ -24179,13 +24179,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -24199,7 +24199,7 @@
         <v>0</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>2723.923475561104</v>
+        <v>2723.923475561105</v>
       </c>
     </row>
     <row r="63">
@@ -24224,49 +24224,49 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>39.09953185359954</v>
+        <v>39.09953185359959</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98857189711013</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.11273231079224</v>
+        <v>32.11273231079223</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20.51692362463237</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>26.7744912852941</v>
+        <v>26.77449128529413</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24305,10 +24305,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -24320,10 +24320,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24617,19 +24617,19 @@
         <v>171</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>169.749838119715</v>
+        <v>169.7498381197151</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>17.77149025158941</v>
@@ -24647,7 +24647,7 @@
         <v>161.058135532108</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>12.81966845609603</v>
@@ -26114,10 +26114,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R90" s="131" t="n">
         <v>15.54712347542384</v>
@@ -26141,7 +26141,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
     </row>
     <row r="91">
@@ -26382,7 +26382,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>0</v>
@@ -26403,7 +26403,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -26650,7 +26650,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>10.9692656257673</v>
@@ -26671,13 +26671,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
     </row>
     <row r="99">
@@ -26702,49 +26702,49 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>44.49156992393183</v>
+        <v>44.49156992393188</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.91479957144558</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.0389599851277</v>
+        <v>39.03895998512768</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>33.98642467644335</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>40.24399233710508</v>
+        <v>40.24399233710511</v>
       </c>
     </row>
     <row r="100">
@@ -26778,10 +26778,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -26793,10 +26793,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -27041,16 +27041,16 @@
         <v>171</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>178.7726587222605</v>
@@ -27071,7 +27071,7 @@
         <v>172.8909201642285</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>12.81966845609603</v>
@@ -28116,7 +28116,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>97701.03174199554</v>
+        <v>97701.03174199555</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>73.90391183428737</v>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>3261.22491731152</v>
+        <v>3261.224917311521</v>
       </c>
     </row>
     <row r="26">
@@ -28270,7 +28270,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>6531.668755170008</v>
+        <v>6531.668755170009</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>9.087539887934609</v>
@@ -29647,7 +29647,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>8594.980611133036</v>
+        <v>8594.980611133034</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>16.2245420212208</v>
@@ -29693,7 +29693,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>9.254144785880076</v>
@@ -29938,10 +29938,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R54" s="131" t="n">
         <v>15.54712347542384</v>
@@ -29965,7 +29965,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -30262,7 +30262,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>0</v>
@@ -30283,7 +30283,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -30465,7 +30465,7 @@
         <v>0</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>3268.708170673324</v>
+        <v>3268.708170673325</v>
       </c>
     </row>
     <row r="61">
@@ -30577,7 +30577,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>10.9692656257673</v>
@@ -30598,13 +30598,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -30643,49 +30643,49 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>39.09953185359954</v>
+        <v>39.09953185359959</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98857189711013</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.11273231079224</v>
+        <v>32.11273231079223</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20.51692362463237</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>26.7744912852941</v>
+        <v>26.77449128529413</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30733,10 +30733,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>23.72313943056918</v>
+        <v>23.72313943056917</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -30748,10 +30748,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>23.47341046087817</v>
+        <v>23.47341046087818</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -31045,19 +31045,19 @@
         <v>171</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>26.65852235308652</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>169.749838119715</v>
+        <v>169.7498381197151</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>17.77149025158941</v>
@@ -31075,7 +31075,7 @@
         <v>161.058135532108</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>12.81966845609603</v>
@@ -32542,10 +32542,10 @@
         <v>24.28157864717123</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>7.341582959679586</v>
+        <v>7.341582959679588</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2.325479157124813</v>
+        <v>2.325479157124814</v>
       </c>
       <c r="R90" s="131" t="n">
         <v>15.54712347542384</v>
@@ -32569,7 +32569,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>26.86480048767565</v>
+        <v>26.86480048767564</v>
       </c>
     </row>
     <row r="91">
@@ -32810,7 +32810,7 @@
         <v>12.76057099474366</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>8.95758060072186</v>
+        <v>8.957580600721862</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>0</v>
@@ -32831,7 +32831,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621815</v>
+        <v>3.528447109621814</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -33078,7 +33078,7 @@
         <v>69.88501719363144</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>0.9141054688139416</v>
+        <v>0.9141054688139418</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>10.9692656257673</v>
@@ -33099,13 +33099,13 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173267</v>
+        <v>53.80881842173265</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>65.27627152800358</v>
+        <v>65.27627152800355</v>
       </c>
     </row>
     <row r="99">
@@ -33130,49 +33130,49 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>6.492663762398191</v>
+        <v>6.49266376239822</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029419</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.542724756611889</v>
+        <v>5.542724756611904</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>44.49156992393183</v>
+        <v>44.49156992393188</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>0.5582212223740193</v>
+        <v>0.5582212223740157</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.08078411315882938</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485155078149262</v>
+        <v>5.485155078149248</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.91479957144558</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.0389599851277</v>
+        <v>39.03895998512768</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>0.5560499977934477</v>
+        <v>0.5560499977934512</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.08279381105870698</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>5.618723851809577</v>
+        <v>5.618723851809605</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>33.98642467644335</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>40.24399233710508</v>
+        <v>40.24399233710511</v>
       </c>
     </row>
     <row r="100">
@@ -33206,10 +33206,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.35392196278232</v>
+        <v>27.35392196278231</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -33221,10 +33221,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>28.37996741866328</v>
+        <v>28.37996741866329</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33469,16 +33469,16 @@
         <v>171</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>14.2579966067437</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>32.05056042341882</v>
+        <v>32.05056042341881</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>178.7726587222605</v>
@@ -33499,7 +33499,7 @@
         <v>172.8909201642285</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>12.81966845609603</v>
